--- a/web/public/forms/anjeon-hwangyeong-bi.xlsx
+++ b/web/public/forms/anjeon-hwangyeong-bi.xlsx
@@ -674,7 +674,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -2848,7 +2848,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="35" t="inlineStr">
@@ -3364,7 +3364,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="35" t="inlineStr">
@@ -4294,7 +4294,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="E1" s="35" t="inlineStr">
@@ -4758,7 +4758,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="D1" s="35" t="inlineStr">

--- a/web/public/forms/anjeon-hwangyeong-bi.xlsx
+++ b/web/public/forms/anjeon-hwangyeong-bi.xlsx
@@ -658,7 +658,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -1079,7 +1079,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="E1" s="2" t="inlineStr">
@@ -2034,7 +2034,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
